--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130142366</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130142390</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130142377</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130142437</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130142402</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>130142384</v>
       </c>
       <c r="B9" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>130142410</v>
       </c>
       <c r="B10" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142423</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130142366</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130142390</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130142377</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130142350</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130142437</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130142402</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>130142384</v>
       </c>
       <c r="B9" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>130142410</v>
       </c>
       <c r="B10" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142437</v>
+        <v>130142402</v>
       </c>
       <c r="B7" t="n">
         <v>98920</v>
@@ -1265,7 +1265,7 @@
         <v>594084</v>
       </c>
       <c r="R7" t="n">
-        <v>6428024</v>
+        <v>6428073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142402</v>
+        <v>130142437</v>
       </c>
       <c r="B8" t="n">
         <v>98920</v>
@@ -1371,7 +1371,7 @@
         <v>594084</v>
       </c>
       <c r="R8" t="n">
-        <v>6428073</v>
+        <v>6428024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142402</v>
+        <v>130142437</v>
       </c>
       <c r="B7" t="n">
         <v>98920</v>
@@ -1265,7 +1265,7 @@
         <v>594084</v>
       </c>
       <c r="R7" t="n">
-        <v>6428073</v>
+        <v>6428024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142437</v>
+        <v>130142402</v>
       </c>
       <c r="B8" t="n">
         <v>98920</v>
@@ -1371,7 +1371,7 @@
         <v>594084</v>
       </c>
       <c r="R8" t="n">
-        <v>6428024</v>
+        <v>6428073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142423</v>
+        <v>130142366</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594071</v>
+        <v>594089</v>
       </c>
       <c r="R2" t="n">
-        <v>6428056</v>
+        <v>6428106</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,42 +781,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130142366</v>
+        <v>130142423</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594089</v>
+        <v>594071</v>
       </c>
       <c r="R3" t="n">
-        <v>6428106</v>
+        <v>6428056</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142366</v>
+        <v>130142423</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594089</v>
+        <v>594071</v>
       </c>
       <c r="R2" t="n">
-        <v>6428106</v>
+        <v>6428056</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,46 +784,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130142423</v>
+        <v>130142366</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594071</v>
+        <v>594089</v>
       </c>
       <c r="R3" t="n">
-        <v>6428056</v>
+        <v>6428106</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,7 +893,7 @@
         <v>130142390</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130142377</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142402</v>
+        <v>130142437</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>594084</v>
       </c>
       <c r="R7" t="n">
-        <v>6428073</v>
+        <v>6428024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142437</v>
+        <v>130142402</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>594084</v>
       </c>
       <c r="R8" t="n">
-        <v>6428024</v>
+        <v>6428073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
         <v>130142384</v>
       </c>
       <c r="B9" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>130142410</v>
       </c>
       <c r="B10" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142423</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130142366</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130142390</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130142377</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130142350</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130142437</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130142402</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142384</v>
+        <v>130142410</v>
       </c>
       <c r="B9" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594075</v>
+        <v>594084</v>
       </c>
       <c r="R9" t="n">
-        <v>6428074</v>
+        <v>6428064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142410</v>
+        <v>130142384</v>
       </c>
       <c r="B10" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594084</v>
+        <v>594075</v>
       </c>
       <c r="R10" t="n">
-        <v>6428064</v>
+        <v>6428074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -1431,7 +1431,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142410</v>
+        <v>130142384</v>
       </c>
       <c r="B9" t="n">
         <v>106016</v>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594084</v>
+        <v>594075</v>
       </c>
       <c r="R9" t="n">
-        <v>6428064</v>
+        <v>6428074</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142384</v>
+        <v>130142410</v>
       </c>
       <c r="B10" t="n">
         <v>106016</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594075</v>
+        <v>594084</v>
       </c>
       <c r="R10" t="n">
-        <v>6428074</v>
+        <v>6428064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130142366</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130142390</v>
       </c>
       <c r="B4" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130142377</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130142437</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130142402</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>130142384</v>
       </c>
       <c r="B9" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>130142410</v>
       </c>
       <c r="B10" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60670-2025 artfynd.xlsx
+++ b/artfynd/A 60670-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142423</v>
+        <v>130142390</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594071</v>
+        <v>594075</v>
       </c>
       <c r="R2" t="n">
-        <v>6428056</v>
+        <v>6428074</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +759,18 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,42 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130142366</v>
+        <v>130142441</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,7 +838,7 @@
         <v>594089</v>
       </c>
       <c r="R3" t="n">
-        <v>6428106</v>
+        <v>6427986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130142390</v>
+        <v>130142350</v>
       </c>
       <c r="B4" t="n">
-        <v>92190</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -923,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594075</v>
+        <v>594148</v>
       </c>
       <c r="R4" t="n">
-        <v>6428074</v>
+        <v>6428093</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,18 +983,12 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,42 +1007,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130142377</v>
+        <v>130142423</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594075</v>
+        <v>594071</v>
       </c>
       <c r="R5" t="n">
-        <v>6428074</v>
+        <v>6428056</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,46 +1116,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142350</v>
+        <v>130142359</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,13 +1159,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594148</v>
+        <v>594071</v>
       </c>
       <c r="R6" t="n">
-        <v>6428093</v>
+        <v>6428119</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,6 +1203,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142437</v>
+        <v>130142366</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594084</v>
+        <v>594089</v>
       </c>
       <c r="R7" t="n">
-        <v>6428024</v>
+        <v>6428106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142402</v>
+        <v>130142377</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594084</v>
+        <v>594075</v>
       </c>
       <c r="R8" t="n">
-        <v>6428073</v>
+        <v>6428074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142384</v>
+        <v>130142402</v>
       </c>
       <c r="B9" t="n">
-        <v>106017</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594075</v>
+        <v>594084</v>
       </c>
       <c r="R9" t="n">
-        <v>6428074</v>
+        <v>6428073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,32 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142410</v>
+        <v>130142437</v>
       </c>
       <c r="B10" t="n">
-        <v>106017</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,7 +1586,7 @@
         <v>594084</v>
       </c>
       <c r="R10" t="n">
-        <v>6428064</v>
+        <v>6428024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,6 +1643,218 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130142384</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 60670, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>594075</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6428074</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130142410</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 60670, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594084</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6428064</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
